--- a/UFC_Predictions1.xlsx
+++ b/UFC_Predictions1.xlsx
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.7300089542205548</v>
+        <v>0.7300362313651976</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -546,16 +546,16 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.3944737768931938</v>
+        <v>0.4043242110621548</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.3175657351860993</v>
+        <v>0.3087242843013381</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3944737768931938</v>
+        <v>0.4043242110621548</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2879604879207071</v>
+        <v>0.2869515046365073</v>
       </c>
     </row>
     <row r="3">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.4001036122672247</v>
+        <v>0.4068671394468218</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.4001036122672247</v>
+        <v>0.4068671394468218</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.3119222627780729</v>
+        <v>0.3095196792447047</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2879741249547024</v>
+        <v>0.2836131813084735</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.7417109894662948</v>
+        <v>0.7417070451124361</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.4510369963061556</v>
+        <v>0.4611195816349675</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.3621799342872671</v>
+        <v>0.3565606655122258</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4510369963061556</v>
+        <v>0.4611195816349675</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1867830694065774</v>
+        <v>0.1823197528528067</v>
       </c>
     </row>
     <row r="5">
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.5172831767055414</v>
+        <v>0.5288515977554403</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.5172831767055414</v>
+        <v>0.5288515977554403</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.2793324766579928</v>
+        <v>0.2795293179237342</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.203384346636466</v>
+        <v>0.1916190843208255</v>
       </c>
     </row>
     <row r="6">
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4114531406485919</v>
+        <v>0.4288494658911164</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.4008107295588275</v>
+        <v>0.3866542172437376</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.1877361297925806</v>
+        <v>0.1844963168651459</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.4114531406485919</v>
+        <v>0.4288494658911164</v>
       </c>
     </row>
     <row r="7">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.3747624737732682</v>
+        <v>0.3842363477435119</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.3747624737732682</v>
+        <v>0.3842363477435119</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.3680627008585923</v>
+        <v>0.3599536283722956</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2571748253681395</v>
+        <v>0.2558100238841926</v>
       </c>
     </row>
     <row r="8">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.4728816422563453</v>
+        <v>0.4760536060017153</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.4728816422563453</v>
+        <v>0.4760536060017153</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3104782800932925</v>
+        <v>0.2925650650009316</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.2166400776503622</v>
+        <v>0.2313813289973531</v>
       </c>
     </row>
     <row r="9">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.5492383383616546</v>
+        <v>0.5261255497822557</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.5492383383616546</v>
+        <v>0.5261255497822557</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.2384490672860732</v>
+        <v>0.2445823592976951</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.2123125943522723</v>
+        <v>0.2292920909200493</v>
       </c>
     </row>
     <row r="10">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.4356816866011018</v>
+        <v>0.4457755372399388</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.4356816866011018</v>
+        <v>0.4457755372399388</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.2416365470488457</v>
+        <v>0.2326753091577341</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3226817663500525</v>
+        <v>0.321549153602327</v>
       </c>
     </row>
     <row r="11">
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.360129488593488</v>
+        <v>0.3587081984296777</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.3590075120876378</v>
+        <v>0.3572242711751051</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2808629993188742</v>
+        <v>0.2840675303952173</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.360129488593488</v>
+        <v>0.3587081984296777</v>
       </c>
     </row>
     <row r="12">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.6354122833111832</v>
+        <v>0.6130829576129694</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6354122833111832</v>
+        <v>0.6130829576129694</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.2123847921696026</v>
+        <v>0.2213822498301171</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1522029245192142</v>
+        <v>0.1655347925569134</v>
       </c>
     </row>
     <row r="13">
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.4153989805338932</v>
+        <v>0.4160559384643788</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.4153989805338932</v>
+        <v>0.4160559384643788</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.2720030353759185</v>
+        <v>0.272404518856769</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.3125979840901884</v>
+        <v>0.3115395426788522</v>
       </c>
     </row>
     <row r="14">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.6518113157478416</v>
+        <v>0.6518636830082121</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.4277387922690624</v>
+        <v>0.4366566121359441</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.4277387922690624</v>
+        <v>0.4366566121359441</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.3204235440062617</v>
+        <v>0.3220261859341025</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.251837663724676</v>
+        <v>0.2413172019299533</v>
       </c>
     </row>
     <row r="15">
@@ -1092,16 +1092,16 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.466743903180222</v>
+        <v>0.4710645030078833</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.466743903180222</v>
+        <v>0.4710645030078833</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.3497522267695833</v>
+        <v>0.3515596405250135</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.1835038700501948</v>
+        <v>0.1773758564671031</v>
       </c>
     </row>
     <row r="16">
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4328936073263024</v>
+        <v>0.4609870508459366</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.4302514206740575</v>
+        <v>0.4247150168070106</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.4328936073263024</v>
+        <v>0.4609870508459366</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.1368549719996401</v>
+        <v>0.1142979323470528</v>
       </c>
     </row>
     <row r="17">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.5245884256208365</v>
+        <v>0.554249041211995</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.2409828792700729</v>
+        <v>0.2328148432871099</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.2344286951090906</v>
+        <v>0.2129361155008951</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.5245884256208365</v>
+        <v>0.554249041211995</v>
       </c>
     </row>
     <row r="18">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4042173914037051</v>
+        <v>0.4165526768819658</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.3513495038858704</v>
+        <v>0.3493179400593907</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4042173914037051</v>
+        <v>0.4165526768819658</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2444331047104245</v>
+        <v>0.2341293830586435</v>
       </c>
     </row>
     <row r="19">
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.5061870498118581</v>
+        <v>0.5157742878923512</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.5061870498118581</v>
+        <v>0.5157742878923512</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3060138432879275</v>
+        <v>0.3207794858879392</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1877991069002144</v>
+        <v>0.1634462262197096</v>
       </c>
     </row>
     <row r="20">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.5406325385661731</v>
+        <v>0.5406098717482262</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.6130000339949968</v>
+        <v>0.6294319984311053</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.2188540004933933</v>
+        <v>0.2183116152028635</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.16814596551161</v>
+        <v>0.1522563863660311</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.6130000339949968</v>
+        <v>0.6294319984311053</v>
       </c>
     </row>
     <row r="21">
@@ -1344,16 +1344,16 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4633118495637241</v>
+        <v>0.4748980725035021</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4633118495637241</v>
+        <v>0.4748980725035021</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3564101889221741</v>
+        <v>0.3481913113301132</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.180277961514102</v>
+        <v>0.1769106161663847</v>
       </c>
     </row>
     <row r="22">
@@ -1386,16 +1386,16 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.4243286560229992</v>
+        <v>0.4189658518836815</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3615547549914201</v>
+        <v>0.3666868550187426</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.4243286560229992</v>
+        <v>0.4189658518836815</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2141165889855808</v>
+        <v>0.2143472930975758</v>
       </c>
     </row>
     <row r="23">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4674750152922416</v>
+        <v>0.497849441366465</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.267708293005936</v>
+        <v>0.2695053198418657</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.4674750152922416</v>
+        <v>0.497849441366465</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.2648166917018225</v>
+        <v>0.2326452387916694</v>
       </c>
     </row>
     <row r="24">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4700062447293746</v>
+        <v>0.4768793080630382</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4700062447293746</v>
+        <v>0.4768793080630382</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3345603294212835</v>
+        <v>0.3451228492937986</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1954334258493419</v>
+        <v>0.1779978426431631</v>
       </c>
     </row>
     <row r="25">
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.6267597228579985</v>
+        <v>0.6302064059785022</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.2534902485730732</v>
+        <v>0.2609303208876813</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.6267597228579985</v>
+        <v>0.6302064059785022</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1197500285689282</v>
+        <v>0.1088632731338165</v>
       </c>
     </row>
     <row r="26">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.6209201974519626</v>
+        <v>0.6208633792701445</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.503728140246999</v>
+        <v>0.5254411452404949</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3129234537896571</v>
+        <v>0.3037853014401798</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.503728140246999</v>
+        <v>0.5254411452404949</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1833484059633438</v>
+        <v>0.1707735533193253</v>
       </c>
     </row>
     <row r="27">
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4357643586830883</v>
+        <v>0.4367488697308461</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3004539172445134</v>
+        <v>0.3019687337331926</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.4357643586830883</v>
+        <v>0.4367488697308461</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.2637817240723982</v>
+        <v>0.2612823965359612</v>
       </c>
     </row>
     <row r="28">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.5540769994917737</v>
+        <v>0.5541281024493981</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1638,16 +1638,16 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.5475747712921252</v>
+        <v>0.5667568428438491</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.315680994068468</v>
+        <v>0.3173091666775379</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.5475747712921252</v>
+        <v>0.5667568428438491</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.1367442346394068</v>
+        <v>0.1159339904786131</v>
       </c>
     </row>
     <row r="29">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.8928038464292176</v>
+        <v>0.8927930033667399</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3856650360929598</v>
+        <v>0.3911764360585434</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3856650360929598</v>
+        <v>0.3911764360585434</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3124201993729589</v>
+        <v>0.3300641087918723</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.3019147645340813</v>
+        <v>0.2787594551495843</v>
       </c>
     </row>
     <row r="30">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.804818512521833</v>
+        <v>0.8048185125218328</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -1722,16 +1722,16 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.5140901762435517</v>
+        <v>0.5023267817425876</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.5140901762435517</v>
+        <v>0.5023267817425876</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.2404501871463513</v>
+        <v>0.2551626747442661</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.245459636610097</v>
+        <v>0.2425105435131464</v>
       </c>
     </row>
     <row r="31">
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.5300491250547574</v>
+        <v>0.5300846632181957</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -1764,16 +1764,16 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3510577784997985</v>
+        <v>0.3561299155733378</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3234609457393139</v>
+        <v>0.3199115770793431</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.3510577784997985</v>
+        <v>0.3561299155733378</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.3254812757608876</v>
+        <v>0.323958507347319</v>
       </c>
     </row>
     <row r="32">
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.4146426123419422</v>
+        <v>0.4171436896205413</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.4146426123419422</v>
+        <v>0.4171436896205413</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.3865590942881074</v>
+        <v>0.3786847925765282</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1987982933699504</v>
+        <v>0.2041715178029304</v>
       </c>
     </row>
     <row r="33">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.5362267731865782</v>
+        <v>0.5509290068122349</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.2621050768247021</v>
+        <v>0.2591577478948122</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.2016681499887197</v>
+        <v>0.189913245292953</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.5362267731865782</v>
+        <v>0.5509290068122349</v>
       </c>
     </row>
     <row r="34">
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.4571001915715356</v>
+        <v>0.4578492565134546</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.4226542343845495</v>
+        <v>0.4347130948041256</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.4571001915715356</v>
+        <v>0.4578492565134546</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.1202455740439149</v>
+        <v>0.1074376486824198</v>
       </c>
     </row>
     <row r="35">
@@ -1924,24 +1924,24 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.5319230090252426</v>
+        <v>0.5319230090252425</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>KO/TKO</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.4308993864056666</v>
+        <v>0.4240566325792717</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.4212098467700272</v>
+        <v>0.4240566325792717</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.4308993864056666</v>
+        <v>0.4178557855398307</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.1478907668243063</v>
+        <v>0.1580875818808975</v>
       </c>
     </row>
     <row r="36">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4356987663565048</v>
+        <v>0.4425906962413046</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3512373792960302</v>
+        <v>0.3517321131395202</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2130638543474651</v>
+        <v>0.2056771906191751</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4356987663565048</v>
+        <v>0.4425906962413046</v>
       </c>
     </row>
     <row r="37">
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.4127963578068316</v>
+        <v>0.4210632333309843</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.4127963578068316</v>
+        <v>0.4210632333309843</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.3261065830006993</v>
+        <v>0.3400081547046019</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.2610970591924691</v>
+        <v>0.2389286119644137</v>
       </c>
     </row>
     <row r="38">
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.4626503349772403</v>
+        <v>0.4557576553698564</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2976429657546861</v>
+        <v>0.2953352557783339</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.4626503349772403</v>
+        <v>0.4557576553698564</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.2397066992680737</v>
+        <v>0.2489070888518096</v>
       </c>
     </row>
     <row r="39">
@@ -2100,16 +2100,16 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.533313669633135</v>
+        <v>0.5390150881007425</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2866185194161627</v>
+        <v>0.2896131800205896</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.533313669633135</v>
+        <v>0.5390150881007425</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1800678109507025</v>
+        <v>0.1713717318786679</v>
       </c>
     </row>
     <row r="40">
@@ -2142,16 +2142,16 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.4882677474937939</v>
+        <v>0.4850175591516187</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.251104942842453</v>
+        <v>0.2437862421209926</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2606273096637532</v>
+        <v>0.2711961987273887</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.4882677474937939</v>
+        <v>0.4850175591516187</v>
       </c>
     </row>
     <row r="41">
@@ -2184,16 +2184,16 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.408604500971379</v>
+        <v>0.3955371100899356</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.408604500971379</v>
+        <v>0.3955371100899356</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3161248009302924</v>
+        <v>0.3170112482112941</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.2752706980983287</v>
+        <v>0.2874516416987704</v>
       </c>
     </row>
     <row r="42">
@@ -2226,16 +2226,16 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.3545918575712775</v>
+        <v>0.3583122132289444</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.3507470020348709</v>
+        <v>0.3518998151992178</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.2946611403938517</v>
+        <v>0.2897879715718379</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.3545918575712775</v>
+        <v>0.3583122132289444</v>
       </c>
     </row>
     <row r="43">
@@ -2268,16 +2268,16 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.4068595262289555</v>
+        <v>0.4097698144871236</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.3774059277847491</v>
+        <v>0.3787599257958709</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2157345459862955</v>
+        <v>0.2114702597170054</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.4068595262289555</v>
+        <v>0.4097698144871236</v>
       </c>
     </row>
     <row r="44">
@@ -2310,16 +2310,16 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.3811984836454824</v>
+        <v>0.3808807428550595</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.3811984836454824</v>
+        <v>0.3808807428550595</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2856179064837761</v>
+        <v>0.271718116503734</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.3331836098707414</v>
+        <v>0.3474011406412065</v>
       </c>
     </row>
     <row r="45">
@@ -2352,16 +2352,16 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.4273061348279422</v>
+        <v>0.4441609741086208</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.4273061348279422</v>
+        <v>0.4441609741086208</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.381184791724599</v>
+        <v>0.3765292620232202</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1915090734474589</v>
+        <v>0.179309763868159</v>
       </c>
     </row>
     <row r="46">
@@ -2394,16 +2394,16 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.6138903265120935</v>
+        <v>0.594694281383791</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.6138903265120935</v>
+        <v>0.594694281383791</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.2782126135838613</v>
+        <v>0.287891192624999</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1078970599040452</v>
+        <v>0.1174145259912101</v>
       </c>
     </row>
     <row r="47">
@@ -2436,16 +2436,16 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.4431046702746694</v>
+        <v>0.4490755914963143</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.4431046702746694</v>
+        <v>0.4490755914963143</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.3519155668778766</v>
+        <v>0.3670795952711722</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.2049797628474541</v>
+        <v>0.1838448132325136</v>
       </c>
     </row>
     <row r="48">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.4595846955626069</v>
+        <v>0.4698757364434357</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.4595846955626069</v>
+        <v>0.4698757364434357</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.3212774906488512</v>
+        <v>0.3264577620935344</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.2191378137885419</v>
+        <v>0.2036665014630298</v>
       </c>
     </row>
     <row r="49">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.5674825737424555</v>
+        <v>0.5677256005056562</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.4385752510093616</v>
+        <v>0.4673966045254343</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.3532727730900642</v>
+        <v>0.3529105429168623</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.4385752510093616</v>
+        <v>0.4673966045254343</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.2081519759005742</v>
+        <v>0.1796928525577034</v>
       </c>
     </row>
     <row r="50">
@@ -2562,16 +2562,16 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.4803559150618449</v>
+        <v>0.4950307852969377</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2934146251590646</v>
+        <v>0.2891031328783232</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.4803559150618449</v>
+        <v>0.4950307852969377</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.2262294597790906</v>
+        <v>0.2158660818247392</v>
       </c>
     </row>
     <row r="51">
@@ -2600,20 +2600,20 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>KO/TKO</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.4076928672008562</v>
+        <v>0.4240799125470121</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.4076928672008562</v>
+        <v>0.4205774470430339</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.4025174273000353</v>
+        <v>0.4240799125470121</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.1897897054991085</v>
+        <v>0.1553426404099541</v>
       </c>
     </row>
     <row r="52">
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.7619555842882388</v>
+        <v>0.7619555842882387</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.4725672809084747</v>
+        <v>0.4808443022065283</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.4725672809084747</v>
+        <v>0.4808443022065283</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.3999709289721102</v>
+        <v>0.3972137058385262</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.1274617901194151</v>
+        <v>0.1219419919549455</v>
       </c>
     </row>
     <row r="53">
@@ -2688,16 +2688,16 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.4790583458041908</v>
+        <v>0.4882639468331861</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2940200934348652</v>
+        <v>0.2946290876197727</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.4790583458041908</v>
+        <v>0.4882639468331861</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.226921560760944</v>
+        <v>0.2171069655470411</v>
       </c>
     </row>
     <row r="54">
@@ -2730,16 +2730,16 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.578629282416196</v>
+        <v>0.578060286415647</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2614316377095687</v>
+        <v>0.260143384940891</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.578629282416196</v>
+        <v>0.578060286415647</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1599390798742353</v>
+        <v>0.1617963286434621</v>
       </c>
     </row>
     <row r="55">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.5316749028132707</v>
+        <v>0.5317165694799374</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -2772,16 +2772,16 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.4270269055700615</v>
+        <v>0.4368764008545787</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.3218138175668079</v>
+        <v>0.3184703172072129</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.2511592768631308</v>
+        <v>0.2446532819382083</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.4270269055700615</v>
+        <v>0.4368764008545787</v>
       </c>
     </row>
     <row r="56">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.5825380455937769</v>
+        <v>0.582538045593777</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.5730690193646414</v>
+        <v>0.5789494899654086</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2792788979023957</v>
+        <v>0.2818017840232386</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1476520827329629</v>
+        <v>0.1392487260113528</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.5730690193646414</v>
+        <v>0.5789494899654086</v>
       </c>
     </row>
     <row r="57">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.8667365560968988</v>
+        <v>0.8667678555780025</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -2856,16 +2856,16 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.5362082156828401</v>
+        <v>0.5380454613216286</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2851888292991339</v>
+        <v>0.2936360445793311</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1786029550180262</v>
+        <v>0.1683184940990404</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.5362082156828401</v>
+        <v>0.5380454613216286</v>
       </c>
     </row>
     <row r="58">
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.3474567229216211</v>
+        <v>0.3466174208641368</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.3474567229216211</v>
+        <v>0.3466174208641368</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.3066835066019871</v>
+        <v>0.3082393853728928</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.3458597704763918</v>
+        <v>0.3451431937629704</v>
       </c>
     </row>
     <row r="59">
@@ -2932,24 +2932,24 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.6806975881925674</v>
+        <v>0.6806975881925673</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>KO/TKO</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.4041135738114822</v>
+        <v>0.4020413432501217</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.3930993323026918</v>
+        <v>0.4020413432501217</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.4041135738114822</v>
+        <v>0.3982939894541359</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.2027870938858259</v>
+        <v>0.1996646672957424</v>
       </c>
     </row>
     <row r="60">
@@ -2982,16 +2982,16 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.4289248550393109</v>
+        <v>0.4238627551399149</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.282527350061184</v>
+        <v>0.2859492965309222</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.2885477948995052</v>
+        <v>0.2901879483291627</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.4289248550393109</v>
+        <v>0.4238627551399149</v>
       </c>
     </row>
     <row r="61">
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.3756822935837073</v>
+        <v>0.3763537002428284</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2625016658605386</v>
+        <v>0.2634712829205562</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.3756822935837073</v>
+        <v>0.3763537002428284</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.3618160405557541</v>
+        <v>0.3601750168366154</v>
       </c>
     </row>
     <row r="62">
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.4111392131045958</v>
+        <v>0.3968653990643987</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.3935878987986738</v>
+        <v>0.3921806217034249</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.4111392131045958</v>
+        <v>0.3968653990643987</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.1952728880967306</v>
+        <v>0.2109539792321763</v>
       </c>
     </row>
     <row r="63">
@@ -3104,20 +3104,20 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>KO/TKO</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.421049137772819</v>
+        <v>0.4000759021096476</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.396436811463075</v>
+        <v>0.4000759021096476</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.421049137772819</v>
+        <v>0.3969575213451472</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1825140507641059</v>
+        <v>0.2029665765452053</v>
       </c>
     </row>
     <row r="64">
@@ -3150,16 +3150,16 @@
         </is>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.5088911643040285</v>
+        <v>0.5094195238886954</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.3097472887742276</v>
+        <v>0.3157096761014602</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.5088911643040285</v>
+        <v>0.5094195238886954</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.1813615469217438</v>
+        <v>0.1748708000098446</v>
       </c>
     </row>
     <row r="65">
@@ -3192,16 +3192,16 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.4022085929144922</v>
+        <v>0.3958136597087966</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.2320902753839474</v>
+        <v>0.2294266580629882</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.3657011317015604</v>
+        <v>0.3747596822282152</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.4022085929144922</v>
+        <v>0.3958136597087966</v>
       </c>
     </row>
     <row r="66">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.618034784174278</v>
+        <v>0.6180695063965003</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3234,16 +3234,16 @@
         </is>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.4903283406594561</v>
+        <v>0.4919495559879907</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.3893064760378537</v>
+        <v>0.3924981411037994</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.4903283406594561</v>
+        <v>0.4919495559879907</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.1203651833026902</v>
+        <v>0.1155523029082099</v>
       </c>
     </row>
     <row r="67">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0.7338383798698978</v>
+        <v>0.7338383798698976</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.4358606095322116</v>
+        <v>0.454409470439497</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.2722425993332955</v>
+        <v>0.2733169829187783</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.4358606095322116</v>
+        <v>0.454409470439497</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.291896791134493</v>
+        <v>0.2722735466417248</v>
       </c>
     </row>
     <row r="68">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.7388231317438104</v>
+        <v>0.7388269920899497</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -3318,16 +3318,16 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.4778349931606708</v>
+        <v>0.4784854784710727</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.4778349931606708</v>
+        <v>0.4784854784710727</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.3577122359617216</v>
+        <v>0.380958987095302</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.1644527708776077</v>
+        <v>0.1405555344336254</v>
       </c>
     </row>
   </sheetData>
